--- a/files/DATA/Relics_data.xlsx
+++ b/files/DATA/Relics_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{576A63BB-80D7-41A8-833F-78DA58341BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F627197-5327-4565-A924-00AF32271DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11085" yWindow="2610" windowWidth="27990" windowHeight="14415" xr2:uid="{8C833159-908F-4571-92A8-0C1007759DCC}"/>
+    <workbookView xWindow="-195" yWindow="675" windowWidth="26205" windowHeight="14850" xr2:uid="{8C833159-908F-4571-92A8-0C1007759DCC}"/>
   </bookViews>
   <sheets>
     <sheet name="drops" sheetId="1" r:id="rId1"/>
@@ -2295,19 +2295,19 @@
         <v>68</v>
       </c>
       <c r="C41" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D41" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E41" s="1">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F41" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="G41" s="1">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H41" t="s">
         <v>83</v>
@@ -2318,19 +2318,19 @@
         <v>69</v>
       </c>
       <c r="C42" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D42" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E42" s="1">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="F42" s="1">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="G42" s="1">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="H42" t="s">
         <v>84</v>

--- a/files/DATA/Relics_data.xlsx
+++ b/files/DATA/Relics_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F627197-5327-4565-A924-00AF32271DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B1B5E8-0311-4325-BE72-D3ECEFDCD012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-195" yWindow="675" windowWidth="26205" windowHeight="14850" xr2:uid="{8C833159-908F-4571-92A8-0C1007759DCC}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="140">
   <si>
     <t>探索時に見つかるもの</t>
     <rPh sb="0" eb="2">
@@ -1227,6 +1227,43 @@
     <rPh sb="9" eb="10">
       <t>ハヤ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宝石、レリクスの強化及び合成にはSPも使用します。</t>
+    <rPh sb="0" eb="2">
+      <t>ホウセキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>オヨ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ゴウセイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2~4個</t>
+    <rPh sb="3" eb="4">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1～3個</t>
+    <rPh sb="3" eb="4">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>￥</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1355,7 +1392,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1402,6 +1439,21 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1725,7 +1777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76802377-12B2-484E-B650-8ED954609AD0}">
-  <dimension ref="A1:I113"/>
+  <dimension ref="A1:S122"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
@@ -1858,27 +1910,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B18" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B19" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B20" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B21" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
         <v>73</v>
       </c>
@@ -1907,7 +1959,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
         <v>95</v>
       </c>
@@ -1935,8 +1987,11 @@
       <c r="I24" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="K24" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
         <v>106</v>
       </c>
@@ -1964,8 +2019,33 @@
       <c r="I25" s="9" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="K25" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="S25" s="17"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
         <v>71</v>
       </c>
@@ -1993,8 +2073,32 @@
       <c r="I26" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="K26" s="1">
+        <v>5</v>
+      </c>
+      <c r="L26" s="1">
+        <v>25</v>
+      </c>
+      <c r="M26" s="1">
+        <v>125</v>
+      </c>
+      <c r="N26" s="1">
+        <v>625</v>
+      </c>
+      <c r="O26" s="1">
+        <v>3125</v>
+      </c>
+      <c r="P26" s="1">
+        <v>15625</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>78125</v>
+      </c>
+      <c r="R26" s="1">
+        <v>390625</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B28" s="1" t="s">
         <v>75</v>
       </c>
@@ -2014,7 +2118,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B29" s="2" t="s">
         <v>57</v>
       </c>
@@ -2037,7 +2141,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B30" s="2" t="s">
         <v>58</v>
       </c>
@@ -2060,7 +2164,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B31" s="2" t="s">
         <v>59</v>
       </c>
@@ -2083,7 +2187,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.4">
       <c r="B32" s="2" t="s">
         <v>60</v>
       </c>
@@ -2359,30 +2463,30 @@
         <v>85</v>
       </c>
     </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B44" s="16"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
+    </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A45" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A46" t="s">
-        <v>101</v>
-      </c>
+      <c r="B45" s="16"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="17"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>86</v>
-      </c>
-      <c r="B47" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>86</v>
-      </c>
-      <c r="B48" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.4">
@@ -2390,23 +2494,23 @@
         <v>86</v>
       </c>
       <c r="B49" t="s">
-        <v>26</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>86</v>
+      </c>
+      <c r="B50" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B51" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A52" t="s">
-        <v>87</v>
-      </c>
-      <c r="B52" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.4">
@@ -2414,23 +2518,23 @@
         <v>87</v>
       </c>
       <c r="B53" t="s">
-        <v>29</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A54" t="s">
+        <v>87</v>
+      </c>
+      <c r="B54" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B55" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A56" t="s">
-        <v>88</v>
-      </c>
-      <c r="B56" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.4">
@@ -2438,23 +2542,23 @@
         <v>88</v>
       </c>
       <c r="B57" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A58" t="s">
+        <v>88</v>
+      </c>
+      <c r="B58" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B59" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A60" t="s">
-        <v>89</v>
-      </c>
-      <c r="B60" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.4">
@@ -2462,23 +2566,23 @@
         <v>89</v>
       </c>
       <c r="B61" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A62" t="s">
+        <v>89</v>
+      </c>
+      <c r="B62" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B63" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A64" t="s">
-        <v>90</v>
-      </c>
-      <c r="B64" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.4">
@@ -2486,23 +2590,23 @@
         <v>90</v>
       </c>
       <c r="B65" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A66" t="s">
+        <v>90</v>
+      </c>
+      <c r="B66" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B67" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A68" t="s">
-        <v>91</v>
-      </c>
-      <c r="B68" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.4">
@@ -2510,23 +2614,23 @@
         <v>91</v>
       </c>
       <c r="B69" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A70" t="s">
+        <v>91</v>
+      </c>
+      <c r="B70" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B71" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A72" t="s">
-        <v>92</v>
-      </c>
-      <c r="B72" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.4">
@@ -2534,23 +2638,23 @@
         <v>92</v>
       </c>
       <c r="B73" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A74" t="s">
+        <v>92</v>
+      </c>
+      <c r="B74" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B75" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A76" t="s">
-        <v>93</v>
-      </c>
-      <c r="B76" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.4">
@@ -2558,156 +2662,283 @@
         <v>93</v>
       </c>
       <c r="B77" t="s">
-        <v>47</v>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A78" t="s">
+        <v>93</v>
+      </c>
+      <c r="B78" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A80" t="s">
-        <v>48</v>
+        <v>93</v>
+      </c>
+      <c r="B79" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>51</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A84" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A86" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>53</v>
+        <v>97</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>56</v>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A91" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A94" t="s">
         <v>121</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A93" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A97" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A97" t="s">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A99" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A98" t="s">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A100" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A99" t="s">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A101" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A100" t="s">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A102" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A102" t="s">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A104" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A103" t="s">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A105" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A104" t="s">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A106" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A105" t="s">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A107" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A107" t="s">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A109" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A108" t="s">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A110" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A110" t="s">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A112" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A111" t="s">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A113" t="s">
         <v>86</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B113" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A112" t="s">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A114" t="s">
         <v>87</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B114" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A113" t="s">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A115" t="s">
         <v>133</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B115" t="s">
         <v>132</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B117">
+        <v>10</v>
+      </c>
+      <c r="C117">
+        <v>11</v>
+      </c>
+      <c r="D117">
+        <v>12</v>
+      </c>
+      <c r="E117">
+        <v>13</v>
+      </c>
+      <c r="F117">
+        <v>14</v>
+      </c>
+      <c r="G117">
+        <v>15</v>
+      </c>
+      <c r="H117">
+        <v>16</v>
+      </c>
+      <c r="I117">
+        <v>17</v>
+      </c>
+      <c r="J117">
+        <v>18</v>
+      </c>
+      <c r="K117">
+        <v>19</v>
+      </c>
+      <c r="L117">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A118" t="s">
+        <v>21</v>
+      </c>
+      <c r="B118" t="s">
+        <v>137</v>
+      </c>
+      <c r="C118" t="s">
+        <v>138</v>
+      </c>
+      <c r="D118" t="s">
+        <v>138</v>
+      </c>
+      <c r="E118" t="s">
+        <v>138</v>
+      </c>
+      <c r="F118" t="s">
+        <v>138</v>
+      </c>
+      <c r="G118" t="s">
+        <v>138</v>
+      </c>
+      <c r="H118" t="s">
+        <v>138</v>
+      </c>
+      <c r="I118" t="s">
+        <v>138</v>
+      </c>
+      <c r="J118" t="s">
+        <v>138</v>
+      </c>
+      <c r="K118" t="s">
+        <v>138</v>
+      </c>
+      <c r="L118" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A119" t="s">
+        <v>22</v>
+      </c>
+      <c r="B119" s="19">
+        <v>0.1</v>
+      </c>
+      <c r="C119" s="19">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A120" t="s">
+        <v>16</v>
+      </c>
+      <c r="B120" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="C120" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A121" t="s">
+        <v>17</v>
+      </c>
+      <c r="B121" s="19">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A122" t="s">
+        <v>18</v>
+      </c>
+      <c r="B122" s="20">
+        <v>1E-3</v>
       </c>
     </row>
   </sheetData>

--- a/files/DATA/Relics_data.xlsx
+++ b/files/DATA/Relics_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.antigravity\game\files\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B1B5E8-0311-4325-BE72-D3ECEFDCD012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC9A8BB4-30BC-4C12-B133-AD9FA0ABAEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-195" yWindow="675" windowWidth="26205" windowHeight="14850" xr2:uid="{8C833159-908F-4571-92A8-0C1007759DCC}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="139">
   <si>
     <t>探索時に見つかるもの</t>
     <rPh sb="0" eb="2">
@@ -1260,10 +1260,6 @@
     <rPh sb="3" eb="4">
       <t>コ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>￥</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1777,7 +1773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76802377-12B2-484E-B650-8ED954609AD0}">
-  <dimension ref="A1:S122"/>
+  <dimension ref="A1:S123"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
@@ -2913,6 +2909,33 @@
       <c r="C119" s="19">
         <v>0.2</v>
       </c>
+      <c r="D119" s="19">
+        <v>0.3</v>
+      </c>
+      <c r="E119" s="19">
+        <v>0.4</v>
+      </c>
+      <c r="F119" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="G119" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="H119" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="I119" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="J119" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="K119" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="L119" s="19">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
@@ -2921,8 +2944,35 @@
       <c r="B120" s="19">
         <v>0.05</v>
       </c>
-      <c r="C120" t="s">
-        <v>139</v>
+      <c r="C120" s="19">
+        <v>0.1</v>
+      </c>
+      <c r="D120" s="19">
+        <v>0.15</v>
+      </c>
+      <c r="E120" s="19">
+        <v>0.2</v>
+      </c>
+      <c r="F120" s="19">
+        <v>0.25</v>
+      </c>
+      <c r="G120" s="19">
+        <v>0.3</v>
+      </c>
+      <c r="H120" s="19">
+        <v>0.35</v>
+      </c>
+      <c r="I120" s="19">
+        <v>0.4</v>
+      </c>
+      <c r="J120" s="19">
+        <v>0.45</v>
+      </c>
+      <c r="K120" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="L120" s="19">
+        <v>0.5</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.4">
@@ -2932,6 +2982,36 @@
       <c r="B121" s="19">
         <v>0.01</v>
       </c>
+      <c r="C121" s="19">
+        <v>0.02</v>
+      </c>
+      <c r="D121" s="19">
+        <v>0.03</v>
+      </c>
+      <c r="E121" s="19">
+        <v>0.04</v>
+      </c>
+      <c r="F121" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="G121" s="19">
+        <v>0.06</v>
+      </c>
+      <c r="H121" s="19">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I121" s="19">
+        <v>0.08</v>
+      </c>
+      <c r="J121" s="19">
+        <v>0.09</v>
+      </c>
+      <c r="K121" s="19">
+        <v>0.1</v>
+      </c>
+      <c r="L121" s="19">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
@@ -2939,6 +3019,74 @@
       </c>
       <c r="B122" s="20">
         <v>1E-3</v>
+      </c>
+      <c r="C122" s="20">
+        <v>2E-3</v>
+      </c>
+      <c r="D122" s="20">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="E122" s="20">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="F122" s="20">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G122" s="20">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="H122" s="20">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="I122" s="20">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="J122" s="20">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="K122" s="20">
+        <v>0.01</v>
+      </c>
+      <c r="L122" s="20">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A123" t="s">
+        <v>3</v>
+      </c>
+      <c r="B123" s="19">
+        <v>0.01</v>
+      </c>
+      <c r="C123" s="19">
+        <v>0.02</v>
+      </c>
+      <c r="D123" s="19">
+        <v>0.03</v>
+      </c>
+      <c r="E123" s="19">
+        <v>0.04</v>
+      </c>
+      <c r="F123" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="G123" s="19">
+        <v>0.06</v>
+      </c>
+      <c r="H123" s="19">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I123" s="19">
+        <v>0.08</v>
+      </c>
+      <c r="J123" s="19">
+        <v>0.09</v>
+      </c>
+      <c r="K123" s="19">
+        <v>0.1</v>
+      </c>
+      <c r="L123" s="19">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
